--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142884</v>
+        <v>121142883</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,36 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488766</v>
+        <v>488778</v>
       </c>
       <c r="R3" t="n">
-        <v>6540685</v>
+        <v>6540691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,18 +873,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142883</v>
+        <v>121142884</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>8421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +909,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488778</v>
+        <v>488766</v>
       </c>
       <c r="R4" t="n">
-        <v>6540691</v>
+        <v>6540685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +984,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142883</v>
+        <v>121142884</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,35 +799,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488778</v>
+        <v>488766</v>
       </c>
       <c r="R3" t="n">
-        <v>6540691</v>
+        <v>6540685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +874,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142884</v>
+        <v>121142883</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,36 +916,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488766</v>
+        <v>488778</v>
       </c>
       <c r="R4" t="n">
-        <v>6540685</v>
+        <v>6540691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,18 +990,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142884</v>
+        <v>121142883</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,36 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488766</v>
+        <v>488778</v>
       </c>
       <c r="R3" t="n">
-        <v>6540685</v>
+        <v>6540691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,18 +873,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142883</v>
+        <v>121142884</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>8421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +909,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488778</v>
+        <v>488766</v>
       </c>
       <c r="R4" t="n">
-        <v>6540691</v>
+        <v>6540685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +984,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142883</v>
+        <v>121142884</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>8424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,35 +799,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488778</v>
+        <v>488766</v>
       </c>
       <c r="R3" t="n">
-        <v>6540691</v>
+        <v>6540685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +874,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142884</v>
+        <v>121142883</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,36 +916,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488766</v>
+        <v>488778</v>
       </c>
       <c r="R4" t="n">
-        <v>6540685</v>
+        <v>6540691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,18 +990,12 @@
           <t>2023-10-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112773675</v>
+        <v>121142883</v>
       </c>
       <c r="B2" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarthyttan, Nrk</t>
+          <t>Hallsberg-Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488929</v>
+        <v>488778</v>
       </c>
       <c r="R2" t="n">
-        <v>6540775</v>
+        <v>6540691</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,22 +773,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Björn Almkvist</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142884</v>
+        <v>112773675</v>
       </c>
       <c r="B3" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,17 +820,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Svarthyttan, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488766</v>
+        <v>488929</v>
       </c>
       <c r="R3" t="n">
-        <v>6540685</v>
+        <v>6540775</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,11 +860,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,54 +880,50 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142883</v>
+        <v>121142884</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488778</v>
+        <v>488766</v>
       </c>
       <c r="R4" t="n">
-        <v>6540691</v>
+        <v>6540685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +969,18 @@
           <t>2023-10-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39249-2022 artfynd.xlsx
+++ b/artfynd/A 39249-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142883</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112773675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>